--- a/output/pdf_financials_xlsx/ICRS.xlsx
+++ b/output/pdf_financials_xlsx/ICRS.xlsx
@@ -2659,13 +2659,13 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.05845</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.05845</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.05845</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
@@ -4686,7 +4686,11 @@
           <t>Share based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11935,7 +11939,7 @@
         </is>
       </c>
       <c r="F199" s="5" t="n">
-        <v>0.008477</v>
+        <v>-0.008477</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ICRS.xlsx
+++ b/output/pdf_financials_xlsx/ICRS.xlsx
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.034487</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.04907</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.239135</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -1276,16 +1276,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.034487</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.04907</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.239135</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -1567,13 +1567,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.04907</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.239135</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -7432,7 +7432,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ICRS.xlsx
+++ b/output/pdf_financials_xlsx/ICRS.xlsx
@@ -726,10 +726,10 @@
         <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.068999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.06438099999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1084,10 +1084,10 @@
         <v>-0.191596</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.53424</v>
+        <v>-0.465241</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.124992</v>
+        <v>-0.060611</v>
       </c>
     </row>
     <row r="28">
@@ -1132,10 +1132,10 @@
         <v>-0.191596</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.410826</v>
+        <v>-0.341827</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.051127</v>
+        <v>0.013254</v>
       </c>
     </row>
     <row r="30">
@@ -1158,10 +1158,10 @@
         <v>-48.81302387200326</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-32.26296896338604</v>
+        <v>-26.84434259722453</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-3.536930334364335</v>
+        <v>0.9169025104478045</v>
       </c>
     </row>
     <row r="31">
@@ -9155,7 +9155,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ICRS.xlsx
+++ b/output/pdf_financials_xlsx/ICRS.xlsx
@@ -492,10 +492,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
@@ -518,10 +516,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -542,10 +538,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
@@ -568,10 +562,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.012573</v>
@@ -592,10 +584,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -616,10 +606,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.000792</v>
@@ -640,10 +628,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.15684</v>
@@ -664,10 +650,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -690,10 +674,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -714,10 +696,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -738,10 +718,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -762,10 +740,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -786,10 +762,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.008477</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.15684</v>
@@ -810,10 +784,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -898,10 +870,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.008477</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.15684</v>
@@ -922,10 +892,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -946,10 +914,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -970,10 +936,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.008477</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.15684</v>
@@ -994,10 +958,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>-0.04</v>
@@ -1020,10 +982,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-0.04</v>
@@ -1072,10 +1032,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.008477</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.15684</v>
@@ -1096,10 +1054,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1120,10 +1076,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.008477</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.15684</v>
@@ -1170,10 +1124,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2810,10 +2762,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.008477</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.15684</v>
@@ -3655,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4565,7 +4515,11 @@
           <t>Lease liabilities (Note 7)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -5419,7 +5373,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -8769,24 +8727,26 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ticket and admissions</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>-0.008477</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -8798,34 +8758,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" s="5" t="n">
-        <v>0.650697</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>0.808247</v>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Food and beverage</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>0.034487</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -8837,32 +8803,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H124" s="5" t="n">
-        <v>0.6226699999999999</v>
-      </c>
-      <c r="I124" s="5" t="n">
-        <v>0.6372719999999999</v>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Revenue total</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8880,38 +8850,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H125" s="5" t="n">
-        <v>1.273367</v>
-      </c>
-      <c r="I125" s="5" t="n">
-        <v>1.445519</v>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cost of sales 19</t>
+          <t>Cash, end of period</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.034487</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -8923,11 +8895,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H126" s="5" t="n">
-        <v>0.849762</v>
-      </c>
-      <c r="I126" s="5" t="n">
-        <v>0.899268</v>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -8943,14 +8919,10 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Ticket and admissions</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -8967,10 +8939,10 @@
         </is>
       </c>
       <c r="H127" s="5" t="n">
-        <v>0.423605</v>
+        <v>0.650697</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>0.546251</v>
+        <v>0.808247</v>
       </c>
     </row>
     <row r="128">
@@ -8981,19 +8953,15 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Operating expenses                                19</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Food and beverage</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -9010,10 +8978,10 @@
         </is>
       </c>
       <c r="H128" s="5" t="n">
-        <v>0.530789</v>
+        <v>0.6226699999999999</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>0.566147</v>
+        <v>0.6372719999999999</v>
       </c>
     </row>
     <row r="129">
@@ -9024,15 +8992,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Operating expenses                                19</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Marketing and business development</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>Revenue total</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -9049,10 +9021,10 @@
         </is>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0.067259</v>
+        <v>1.273367</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>0.040715</v>
+        <v>1.445519</v>
       </c>
     </row>
     <row r="130">
@@ -9063,17 +9035,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Operating expenses                                19</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Operating expenses                                19 total</t>
+          <t>Cost of sales 19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9092,10 +9064,10 @@
         </is>
       </c>
       <c r="H130" s="5" t="n">
-        <v>0.598048</v>
+        <v>0.849762</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>0.606862</v>
+        <v>0.899268</v>
       </c>
     </row>
     <row r="131">
@@ -9106,15 +9078,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Debt forgiveness</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -9131,12 +9107,10 @@
         </is>
       </c>
       <c r="H131" s="5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.423605</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>0.546251</v>
       </c>
     </row>
     <row r="132">
@@ -9147,17 +9121,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses                                19</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Net finance expense</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestExpenseNonOperating</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9176,10 +9150,10 @@
         </is>
       </c>
       <c r="H132" s="5" t="n">
-        <v>0.068999</v>
+        <v>0.530789</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>0.06438099999999999</v>
+        <v>0.566147</v>
       </c>
     </row>
     <row r="133">
@@ -9190,12 +9164,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses                                19</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Impairment of goodwill and intangibles assets 17</t>
+          <t>Marketing and business development</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -9215,12 +9189,10 @@
         </is>
       </c>
       <c r="H133" s="5" t="n">
-        <v>0.310798</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.067259</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>0.040715</v>
       </c>
     </row>
     <row r="134">
@@ -9231,15 +9203,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Operating expenses                                19</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Net other items</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Operating expenses                                19 total</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -9256,10 +9232,10 @@
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>0.359797</v>
+        <v>0.598048</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>0.06438099999999999</v>
+        <v>0.606862</v>
       </c>
     </row>
     <row r="135">
@@ -9275,14 +9251,10 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Income tax expense 9</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Debt forgiveness</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -9299,10 +9271,12 @@
         </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0.00129</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>0.00919</v>
+        <v>-0.02</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -9318,12 +9292,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss)</t>
+          <t>Net finance expense</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestExpenseNonOperating</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9342,10 +9316,10 @@
         </is>
       </c>
       <c r="H136" s="5" t="n">
-        <v>-0.53553</v>
+        <v>0.068999</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>-0.134182</v>
+        <v>0.06438099999999999</v>
       </c>
     </row>
     <row r="137">
@@ -9356,12 +9330,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Number of           Shares to           Convertible Share based</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Balance - January 1, 2025 14 6,567,827 389,342 19,000 19,480 18,351 38,970</t>
+          <t>Impairment of goodwill and intangibles assets 17</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -9381,10 +9355,12 @@
         </is>
       </c>
       <c r="H137" s="5" t="n">
-        <v>-0.410697</v>
-      </c>
-      <c r="I137" s="5" t="n">
-        <v>-0.89584</v>
+        <v>0.310798</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -9395,12 +9371,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Number of           Shares to           Convertible Share based</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Shares issued on private placement 14 2,010,000 196,000 (19,000) - - -</t>
+          <t>Net other items</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -9420,12 +9396,10 @@
         </is>
       </c>
       <c r="H138" s="5" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.359797</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>0.06438099999999999</v>
       </c>
     </row>
     <row r="139">
@@ -9436,15 +9410,19 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Number of           Shares to           Convertible Share based</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Share issuance costs 14 - (15,818) - 13,568 - -</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>Income tax expense 9</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -9461,12 +9439,10 @@
         </is>
       </c>
       <c r="H139" s="5" t="n">
-        <v>-0.00225</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00129</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0.00919</v>
       </c>
     </row>
     <row r="140">
@@ -9477,12 +9453,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Number of           Shares to           Convertible Share based</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - -</t>
+          <t>Net income (loss) and comprehensive income (loss)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9506,7 +9482,7 @@
         </is>
       </c>
       <c r="H140" s="5" t="n">
-        <v>-0.134182</v>
+        <v>-0.53553</v>
       </c>
       <c r="I140" s="5" t="n">
         <v>-0.134182</v>
@@ -9525,7 +9501,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Balance - December 31, 2025 8,577,827 569,524 - 33,048 18,351 38,970</t>
+          <t>Balance - January 1, 2025 14 6,567,827 389,342 19,000 19,480 18,351 38,970</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -9545,10 +9521,10 @@
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>-0.370129</v>
+        <v>-0.410697</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>-1.030022</v>
+        <v>-0.89584</v>
       </c>
     </row>
     <row r="142">
@@ -9564,7 +9540,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Balance - January 1, 2024 14 6,367,827 382,342 - 19,480 14,809 38,970</t>
+          <t>Shares issued on private placement 14 2,010,000 196,000 (19,000) - - -</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -9584,10 +9560,12 @@
         </is>
       </c>
       <c r="H142" s="5" t="n">
-        <v>0.095291</v>
-      </c>
-      <c r="I142" s="5" t="n">
-        <v>-0.36031</v>
+        <v>0.177</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -9603,7 +9581,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Shares issued for right to theatre shows 14 200,000 7,000 - - - -</t>
+          <t>Share issuance costs 14 - (15,818) - 13,568 - -</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -9623,7 +9601,7 @@
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.00225</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -9644,10 +9622,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Convertible debenture 14 - - - - 3,542 -</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -9664,12 +9646,10 @@
         </is>
       </c>
       <c r="H144" s="5" t="n">
-        <v>0.003542</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.134182</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>-0.134182</v>
       </c>
     </row>
     <row r="145">
@@ -9685,7 +9665,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Shares issued for cash 14 - - 19,000 - - -</t>
+          <t>Balance - December 31, 2025 8,577,827 569,524 - 33,048 18,351 38,970</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -9705,12 +9685,10 @@
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.370129</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>-1.030022</v>
       </c>
     </row>
     <row r="146">
@@ -9726,14 +9704,10 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - - -</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance - January 1, 2024 14 6,367,827 382,342 - 19,480 14,809 38,970</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -9750,10 +9724,10 @@
         </is>
       </c>
       <c r="H146" s="5" t="n">
-        <v>-0.53553</v>
+        <v>0.095291</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>-0.53553</v>
+        <v>-0.36031</v>
       </c>
     </row>
     <row r="147">
@@ -9769,7 +9743,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Balance - December 31, 2024 6,567,827 389,342 19,000 19,480 18,351 38,970</t>
+          <t>Shares issued for right to theatre shows 14 200,000 7,000 - - - -</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -9789,10 +9763,12 @@
         </is>
       </c>
       <c r="H147" s="5" t="n">
-        <v>-0.410697</v>
-      </c>
-      <c r="I147" s="5" t="n">
-        <v>-0.89584</v>
+        <v>0.007</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -9803,19 +9779,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Icarus Capital Corp.</t>
+          <t>Number of           Shares to           Convertible Share based</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Convertible debenture 14 - - - - 3,542 -</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -9826,11 +9798,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G148" s="5" t="n">
-        <v>0.39251</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>1.273367</v>
+        <v>0.003542</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -9846,19 +9820,15 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Icarus Capital Corp.</t>
+          <t>Number of           Shares to           Convertible Share based</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Shares issued for cash 14 - - 19,000 - - -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -9869,11 +9839,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G149" s="5" t="n">
-        <v>0.246577</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H149" s="5" t="n">
-        <v>0.849762</v>
+        <v>0.019</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -9889,17 +9861,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Icarus Capital Corp.</t>
+          <t>Number of           Shares to           Convertible Share based</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Net loss and comprehensive loss - - - - - -</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9912,16 +9884,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G150" s="5" t="n">
-        <v>0.145933</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H150" s="5" t="n">
-        <v>0.423605</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.53553</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>-0.53553</v>
       </c>
     </row>
     <row r="151">
@@ -9932,12 +9904,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number of           Shares to           Convertible Share based</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Accretion of interest on lease liabilities</t>
+          <t>Balance - December 31, 2024 6,567,827 389,342 19,000 19,480 18,351 38,970</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -9951,16 +9923,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G151" s="5" t="n">
-        <v>0.000576</v>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H151" s="5" t="n">
-        <v>0.004465</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.410697</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>-0.89584</v>
       </c>
     </row>
     <row r="152">
@@ -9971,15 +9943,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Icarus Capital Corp.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Accretion of interest on long-term loans payable</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -9991,10 +9967,10 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.006994</v>
+        <v>0.39251</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>0.015053</v>
+        <v>1.273367</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -10010,17 +9986,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Icarus Capital Corp.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10034,10 +10010,10 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.00599</v>
+        <v>0.246577</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0.067259</v>
+        <v>0.849762</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -10053,28 +10029,34 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Icarus Capital Corp.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Agency fees</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F154" s="5" t="n">
-        <v>0.005882</v>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.011018</v>
+        <v>0.145933</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>0.013655</v>
+        <v>0.423605</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -10095,14 +10077,10 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Accretion of interest on lease liabilities</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -10114,10 +10092,10 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.018985</v>
+        <v>0.000576</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>0.123414</v>
+        <v>0.004465</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -10138,14 +10116,10 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accretion of interest on long-term loans payable</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -10157,12 +10131,10 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.018203</v>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006994</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>0.015053</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -10183,23 +10155,29 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Dues and subscriptions</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F157" s="5" t="n">
-        <v>0.000777</v>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.001678</v>
+        <v>0.00599</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>0.00425</v>
+        <v>0.067259</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -10220,27 +10198,23 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Agency fees</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.005882</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.010789</v>
+        <v>0.011018</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>0.00953</v>
+        <v>0.013655</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -10261,12 +10235,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10280,10 +10254,10 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.004526</v>
+        <v>0.018985</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>0.020096</v>
+        <v>0.123414</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -10304,7 +10278,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
+          <t>Consulting fees (Note 10)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10317,14 +10291,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F160" s="5" t="n">
-        <v>0.002073</v>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.000969</v>
-      </c>
-      <c r="H160" s="5" t="n">
-        <v>0.009457</v>
+        <v>0.018203</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -10345,7 +10323,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Interest on long-term debt</t>
+          <t>Dues and subscriptions</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -10354,16 +10332,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F161" s="5" t="n">
+        <v>0.000777</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.014937</v>
+        <v>0.001678</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>0.04354</v>
+        <v>0.00425</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -10384,7 +10360,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Management fees (Note 10)</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10397,18 +10373,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F162" s="5" t="n">
+        <v>0.0105</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010789</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>0.00953</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -10429,12 +10401,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10442,14 +10414,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n">
-        <v>0.000792</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.009738</v>
+        <v>0.004526</v>
       </c>
       <c r="H163" s="5" t="n">
-        <v>0.029198</v>
+        <v>0.020096</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -10470,23 +10444,27 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Professional services</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.097846</v>
+        <v>0.002073</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.117283</v>
+        <v>0.000969</v>
       </c>
       <c r="H164" s="5" t="n">
-        <v>0.095128</v>
+        <v>0.009457</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -10507,7 +10485,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Property taxes</t>
+          <t>Interest on long-term debt</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -10522,10 +10500,10 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.00542</v>
+        <v>0.014937</v>
       </c>
       <c r="H165" s="5" t="n">
-        <v>0.016261</v>
+        <v>0.04354</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -10546,7 +10524,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Management fees (Note 10)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10565,10 +10543,12 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.01575</v>
-      </c>
-      <c r="H166" s="5" t="n">
-        <v>0.012737</v>
+        <v>0.045</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -10589,25 +10569,27 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Royalty fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F167" s="5" t="n">
+        <v>0.000792</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.02642</v>
+        <v>0.009738</v>
       </c>
       <c r="H167" s="5" t="n">
-        <v>0.082528</v>
+        <v>0.029198</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -10628,31 +10610,23 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Professional services</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F168" s="5" t="n">
+        <v>0.097846</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.117283</v>
       </c>
       <c r="H168" s="5" t="n">
-        <v>0.07825600000000001</v>
+        <v>0.095128</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -10673,7 +10647,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Telephone and utilities</t>
+          <t>Property taxes</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -10688,10 +10662,10 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.018056</v>
+        <v>0.00542</v>
       </c>
       <c r="H169" s="5" t="n">
-        <v>0.036182</v>
+        <v>0.016261</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -10712,7 +10686,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10731,10 +10705,10 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.005197</v>
+        <v>0.01575</v>
       </c>
       <c r="H170" s="5" t="n">
-        <v>0.006038</v>
+        <v>0.012737</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -10755,27 +10729,25 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Royalty fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F171" s="5" t="n">
-        <v>0.15684</v>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.337529</v>
+        <v>0.02642</v>
       </c>
       <c r="H171" s="5" t="n">
-        <v>0.6670469999999999</v>
+        <v>0.082528</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -10796,12 +10768,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Income (loss) from operations</t>
+          <t>Salaries and benefits</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10814,11 +10786,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" s="5" t="n">
-        <v>-0.191596</v>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>-0.243442</v>
+        <v>0.07825600000000001</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -10834,12 +10808,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Debt forgiveness</t>
+          <t>Telephone and utilities</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -10853,13 +10827,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G173" s="5" t="n">
+        <v>0.018056</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>0.02</v>
+        <v>0.036182</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -10875,15 +10847,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Impairment of goodwill and intangible assets</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -10894,13 +10870,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G174" s="5" t="n">
+        <v>0.005197</v>
       </c>
       <c r="H174" s="5" t="n">
-        <v>-0.310798</v>
+        <v>0.006038</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -10916,32 +10890,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Other income (expense) total</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F175" s="5" t="n">
+        <v>0.15684</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.337529</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>-0.290798</v>
+        <v>0.6670469999999999</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10957,17 +10931,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
+          <t>Income (loss) from operations</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10984,7 +10958,7 @@
         <v>-0.191596</v>
       </c>
       <c r="H176" s="5" t="n">
-        <v>-0.53424</v>
+        <v>-0.243442</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -11005,14 +10979,10 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Income taxes</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Debt forgiveness</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -11023,11 +10993,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G177" s="5" t="n">
-        <v>0.003396</v>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>0.00129</v>
+        <v>0.02</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -11048,14 +11020,10 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Impairment of goodwill and intangible assets</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -11066,11 +11034,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G178" s="5" t="n">
-        <v>-0.194992</v>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>-0.53553</v>
+        <v>-0.310798</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -11091,14 +11061,10 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (Note 14)</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Other income (expense) total</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -11109,11 +11075,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G179" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>-8e-08</v>
+        <v>-0.290798</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -11134,12 +11102,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11153,10 +11121,10 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>6.367827</v>
+        <v>-0.191596</v>
       </c>
       <c r="H180" s="5" t="n">
-        <v>6.567827</v>
+        <v>-0.53424</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -11170,15 +11138,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Income taxes</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11192,12 +11164,10 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>0.39251</v>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003396</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>0.00129</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -11211,15 +11181,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11233,12 +11207,10 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.246577</v>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.194992</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>-0.53553</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -11252,15 +11224,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Basic and diluted loss per share (Note 14)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11274,12 +11250,10 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.145933</v>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>-8e-08</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -11295,32 +11269,34 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Share based compensations (Note 8)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F184" s="5" t="n">
-        <v>0.03897</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>6.367827</v>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>6.567827</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -11334,19 +11310,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11354,11 +11326,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F185" s="5" t="n">
-        <v>-0.15684</v>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>-0.191596</v>
+        <v>0.39251</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -11377,19 +11351,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11403,7 +11373,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.003396</v>
+        <v>0.246577</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -11422,19 +11392,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11442,11 +11408,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F187" s="5" t="n">
-        <v>-0.15684</v>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>-0.194992</v>
+        <v>0.145933</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -11472,24 +11440,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share based compensations (Note 8)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F188" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G188" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.03897</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -11515,12 +11481,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11529,10 +11495,10 @@
         </is>
       </c>
       <c r="F189" s="5" t="n">
-        <v>4</v>
+        <v>-0.15684</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>6.367827</v>
+        <v>-0.191596</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -11551,25 +11517,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>December 31, 2022 from February</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F190" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="n">
+        <v>0.003396</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -11590,27 +11564,29 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>incorporation) to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F191" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.15684</v>
+      </c>
+      <c r="G191" s="5" t="n">
+        <v>-0.194992</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -11631,27 +11607,29 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>incorporation) to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>incorporation) to total</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="G192" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -11672,29 +11650,29 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Agency fees $5,882</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F193" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>6.367827</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -11713,14 +11691,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Banking charges 2,073</t>
+          <t>December 31, 2022 from February</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -11730,7 +11704,7 @@
         </is>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.000152</v>
+        <v>2e-06</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -11756,12 +11730,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>incorporation) to</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Dues and subscriptions 777</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -11770,10 +11744,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F195" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -11799,28 +11771,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>incorporation) to</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Filing fees 10,500</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>incorporation) to total</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F196" s="5" t="n">
+        <v>0.002021</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -11851,7 +11817,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Professional services 97,845</t>
+          <t>Agency fees $5,882</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -11860,8 +11826,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F197" s="5" t="n">
-        <v>0.008325000000000001</v>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -11892,7 +11860,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 8)</t>
+          <t>Banking charges 2,073</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -11902,7 +11870,7 @@
         </is>
       </c>
       <c r="F198" s="5" t="n">
-        <v>0.03897</v>
+        <v>0.000152</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -11933,21 +11901,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss 156,841</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Dues and subscriptions 777</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F199" s="5" t="n">
-        <v>-0.008477</v>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -11978,17 +11944,23 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted 0.08</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Filing fees 10,500</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F200" s="5" t="n">
-        <v>0</v>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -12019,33 +11991,418 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>Professional services 97,845</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>0.008325000000000001</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Share based compensation (Note 8)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss 156,841</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>-0.008477</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted 0.08</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding 2,000,000</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F201" s="5" t="n">
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Banking fees</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" s="5" t="n">
+        <v>0.000152</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Professional services</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.008325000000000001</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>-0.008477</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
